--- a/Data/Data_Model.xlsx
+++ b/Data/Data_Model.xlsx
@@ -3,10 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Energy_data" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Weather_data_per_zone" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Sun_data" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Date_data" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Parameters" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Energy_data" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Weather_data" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="Daily_weather" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="Forecast_data" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="Date_data" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,100 +16,175 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
+  <si>
+    <t>Parameters</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
   <si>
     <t>Timestamp</t>
   </si>
   <si>
-    <t>Energy compsuption</t>
+    <t>Demand_ITSDO</t>
   </si>
   <si>
     <t>Price</t>
   </si>
   <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>MaxTemp</t>
-  </si>
-  <si>
-    <t>MinTemp</t>
-  </si>
-  <si>
-    <t>UvIndex</t>
-  </si>
-  <si>
-    <t>Wind</t>
-  </si>
-  <si>
-    <t>Dew point</t>
-  </si>
-  <si>
-    <t>Cloud cover</t>
-  </si>
-  <si>
-    <t>Wind_speed</t>
-  </si>
-  <si>
-    <t>Pressure</t>
-  </si>
-  <si>
-    <t>Apparent_temp_max</t>
-  </si>
-  <si>
-    <t>Apparent_temp_min</t>
-  </si>
-  <si>
-    <t>Visibility</t>
-  </si>
-  <si>
-    <t>Humidity</t>
-  </si>
-  <si>
-    <t>Moonphase</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Sunset_time</t>
-  </si>
-  <si>
-    <t>Sunrise_time</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Day of week</t>
-  </si>
-  <si>
-    <t>Day of year</t>
-  </si>
-  <si>
-    <t>Week of year</t>
-  </si>
-  <si>
-    <t>Month</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Holidays</t>
-  </si>
-  <si>
-    <t>Working day</t>
-  </si>
-  <si>
-    <t>School day</t>
+    <t>Demand_INDEEM</t>
+  </si>
+  <si>
+    <t>timestamp_utc</t>
+  </si>
+  <si>
+    <t>temperature_2m</t>
+  </si>
+  <si>
+    <t>relative_humidity_2m</t>
+  </si>
+  <si>
+    <t>dew_point_2m</t>
+  </si>
+  <si>
+    <t>precipitation</t>
+  </si>
+  <si>
+    <t>rain</t>
+  </si>
+  <si>
+    <t>showers</t>
+  </si>
+  <si>
+    <t>snowfall</t>
+  </si>
+  <si>
+    <t>wind_speed_10m</t>
+  </si>
+  <si>
+    <t>wind_direction_10m</t>
+  </si>
+  <si>
+    <t>wind_gusts_10m</t>
+  </si>
+  <si>
+    <t>weather_code</t>
+  </si>
+  <si>
+    <t>visibility</t>
+  </si>
+  <si>
+    <t>surface_pressure</t>
+  </si>
+  <si>
+    <t>cloud_cover</t>
+  </si>
+  <si>
+    <t>cloud_cover_low</t>
+  </si>
+  <si>
+    <t>cloud_cover_mid</t>
+  </si>
+  <si>
+    <t>cloud_cover_high</t>
+  </si>
+  <si>
+    <t>direct_radiation</t>
+  </si>
+  <si>
+    <t>shortwave_radiation</t>
+  </si>
+  <si>
+    <t>diffuse_radiation</t>
+  </si>
+  <si>
+    <t>sunshine_duration</t>
+  </si>
+  <si>
+    <t>is_day</t>
+  </si>
+  <si>
+    <t>date_utc</t>
+  </si>
+  <si>
+    <t>precipitation_sum</t>
+  </si>
+  <si>
+    <t>rain_sum</t>
+  </si>
+  <si>
+    <t>snowfall_sum</t>
+  </si>
+  <si>
+    <t>precipitation_hours</t>
+  </si>
+  <si>
+    <t>temperature_2m_max</t>
+  </si>
+  <si>
+    <t>temperature_2m_min</t>
+  </si>
+  <si>
+    <t>sunrise</t>
+  </si>
+  <si>
+    <t>sunset</t>
+  </si>
+  <si>
+    <t>daylight_duration</t>
+  </si>
+  <si>
+    <t>shortwave_radiation_sum</t>
+  </si>
+  <si>
+    <t>Data available</t>
+  </si>
+  <si>
+    <t>https://bmrs.elexon.co.uk/api-documentation/endpoint/forecast</t>
+  </si>
+  <si>
+    <t>Generated by code given the other datasets</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>day_of_week</t>
+  </si>
+  <si>
+    <t>day_of_year</t>
+  </si>
+  <si>
+    <t>week_of_year</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>holidays</t>
+  </si>
+  <si>
+    <t>working_day</t>
+  </si>
+  <si>
+    <t>school_day</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -118,6 +195,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,12 +215,18 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -162,6 +249,14 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -369,39 +464,39 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="16.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
         <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
@@ -413,34 +508,7 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -454,16 +522,102 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="11.88"/>
+    <col customWidth="1" min="2" max="2" width="13.25"/>
+    <col customWidth="1" min="3" max="3" width="16.75"/>
+    <col customWidth="1" min="4" max="4" width="11.88"/>
+    <col customWidth="1" min="5" max="5" width="10.0"/>
+    <col customWidth="1" min="6" max="6" width="3.75"/>
+    <col customWidth="1" min="7" max="7" width="7.25"/>
+    <col customWidth="1" min="8" max="8" width="7.0"/>
+    <col customWidth="1" min="9" max="9" width="14.0"/>
+    <col customWidth="1" min="10" max="10" width="15.88"/>
+    <col customWidth="1" min="11" max="11" width="12.63"/>
+    <col customWidth="1" min="12" max="12" width="11.5"/>
+    <col customWidth="1" min="13" max="13" width="6.75"/>
+    <col customWidth="1" min="14" max="14" width="13.88"/>
+    <col customWidth="1" min="15" max="15" width="10.0"/>
+    <col customWidth="1" min="16" max="16" width="13.38"/>
+    <col customWidth="1" min="17" max="17" width="13.63"/>
+    <col customWidth="1" min="18" max="18" width="14.0"/>
+    <col customWidth="1" min="19" max="19" width="12.38"/>
+    <col customWidth="1" min="20" max="20" width="15.88"/>
+    <col customWidth="1" min="21" max="21" width="13.25"/>
+    <col customWidth="1" min="22" max="22" width="14.63"/>
+    <col customWidth="1" min="23" max="23" width="5.88"/>
+    <col customWidth="1" min="24" max="28" width="12.0"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -477,40 +631,146 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="7.38"/>
+    <col customWidth="1" min="2" max="2" width="11.5"/>
+    <col customWidth="1" min="3" max="3" width="14.0"/>
+    <col customWidth="1" min="4" max="4" width="7.88"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="14.63"/>
+    <col customWidth="1" min="7" max="7" width="17.25"/>
+    <col customWidth="1" min="8" max="8" width="16.88"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="16.0"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="B2"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="33.38"/>
+    <col customWidth="1" min="2" max="2" width="11.5"/>
+    <col customWidth="1" min="3" max="3" width="14.0"/>
+    <col customWidth="1" min="4" max="4" width="9.5"/>
+    <col customWidth="1" min="5" max="5" width="11.13"/>
+    <col customWidth="1" min="6" max="6" width="14.63"/>
+    <col customWidth="1" min="7" max="7" width="17.25"/>
+    <col customWidth="1" min="8" max="8" width="16.88"/>
+    <col customWidth="1" min="9" max="9" width="10.25"/>
+    <col customWidth="1" min="10" max="10" width="9.25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:J1"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>